--- a/bench/results.xlsx
+++ b/bench/results.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\use this for code\chess-engine\bench\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FD7369-9F25-423C-BFCF-8BA4054B3B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E825C42-9603-471D-968C-7831FC38F77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Puzzle Results" sheetId="1" r:id="rId1"/>
-    <sheet name="Node Reduction" sheetId="2" r:id="rId2"/>
+    <sheet name="#19" sheetId="1" r:id="rId1"/>
+    <sheet name="#20" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="185">
   <si>
     <t>#</t>
   </si>
@@ -535,68 +535,71 @@
     <t>Avg Nodes/Puzzle</t>
   </si>
   <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Nodes</t>
-  </si>
-  <si>
-    <t>Reduction vs Minimax</t>
-  </si>
-  <si>
-    <t>Minimax (baseline)</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>Alpha-beta</t>
-  </si>
-  <si>
-    <t>92%</t>
-  </si>
-  <si>
-    <t>Alpha-beta + TT</t>
-  </si>
-  <si>
-    <t>94%</t>
-  </si>
-  <si>
-    <t>AB + TT + Move Ordering</t>
-  </si>
-  <si>
-    <t>97%</t>
-  </si>
-  <si>
-    <t>Depth</t>
-  </si>
-  <si>
-    <t>perft(3)</t>
-  </si>
-  <si>
-    <t>Tests passing</t>
-  </si>
-  <si>
-    <t>33 / 33</t>
+    <t>b5d4</t>
+  </si>
+  <si>
+    <t>f7c7</t>
+  </si>
+  <si>
+    <t>f6h6</t>
+  </si>
+  <si>
+    <t>h2g3</t>
+  </si>
+  <si>
+    <t>e6e5</t>
+  </si>
+  <si>
+    <t>d8g8</t>
+  </si>
+  <si>
+    <t>e7f6</t>
+  </si>
+  <si>
+    <t>d5f4</t>
+  </si>
+  <si>
+    <t>g2h4</t>
+  </si>
+  <si>
+    <t>b7b4</t>
+  </si>
+  <si>
+    <t>e5d4</t>
+  </si>
+  <si>
+    <t>g7f8</t>
+  </si>
+  <si>
+    <t>c3c4</t>
+  </si>
+  <si>
+    <t>f2f4</t>
+  </si>
+  <si>
+    <t>d1c2</t>
+  </si>
+  <si>
+    <t>f8g7</t>
+  </si>
+  <si>
+    <t>f8e8</t>
+  </si>
+  <si>
+    <t>g3f3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -610,51 +613,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -690,57 +659,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1057,2066 +988,2066 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="1">
         <v>87303</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="1">
         <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="1">
         <v>158776</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="1">
         <v>244</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I3" s="16"/>
+      <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="1">
         <v>167855</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="1">
         <v>346</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="1">
         <v>37544</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="1">
         <v>85</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="1">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="1">
         <v>12893</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="1">
         <v>34</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="3">
         <f>COUNTIF(B2:B101,"PASS")/100</f>
         <v>0.38</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="16">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="16" t="s">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="1">
         <v>50685</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="1">
         <v>90</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="1">
         <f>SUM(E2:E101)</f>
         <v>6293672</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="16">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="1">
         <v>244863</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="1">
         <v>532</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="1">
         <f>SUM(F2:F101)</f>
         <v>11282</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="1">
         <v>27180</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="1">
         <v>59</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="1">
         <f>AVERAGE(E2:E101)</f>
         <v>62936.72</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="1">
         <v>168123</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="1">
         <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="1">
         <v>14321</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="1">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="1">
         <v>9644</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="1">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="1">
         <v>19709</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="1">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
-        <v>13</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="1">
         <v>13844</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="1">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="16" t="s">
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="1">
         <v>12855</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="1">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="1">
         <v>111758</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="1">
         <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="16" t="s">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="1">
         <v>72481</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="1">
         <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="1">
         <v>31197</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="1">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="1">
         <v>44826</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="1">
         <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="1">
         <v>44061</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="1">
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="1">
         <v>2797</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="1">
         <v>20158</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="1">
         <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="1">
         <v>19592</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="1">
         <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="1">
         <v>8024</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="1">
         <v>103851</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="1">
         <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="B26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="1">
         <v>10791</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="1">
         <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="1">
         <v>61457</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="1">
         <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="16" t="s">
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="1">
         <v>72562</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="1">
         <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="16">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="16" t="s">
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="1">
         <v>113486</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="1">
         <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="1">
         <v>161998</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="1">
         <v>455</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="B31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="1">
         <v>108988</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="1">
         <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="16">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="B32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="1">
         <v>4037</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="16" t="s">
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="1">
         <v>10292</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="1">
         <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="1">
         <v>43859</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="1">
         <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="16">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="16" t="s">
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="1">
         <v>45869</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="1">
         <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="16">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="1">
         <v>43795</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="1">
         <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="16">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="16" t="s">
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="1">
         <v>67879</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="1">
         <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="16">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="16" t="s">
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="1">
         <v>110983</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="1">
         <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="16">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="1">
         <v>52316</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="1">
         <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="16">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="16" t="s">
+      <c r="B40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="1">
         <v>1662</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="1">
         <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="16">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="1">
         <v>51510</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="1">
         <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="16">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="16" t="s">
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="1">
         <v>49042</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="1">
         <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="16">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="16" t="s">
+      <c r="B43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="1">
         <v>2741</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="16">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="16" t="s">
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="1">
         <v>19531</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="1">
         <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="16">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="16" t="s">
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="1">
         <v>132954</v>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="1">
         <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="16">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="16" t="s">
+      <c r="B46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="1">
         <v>10908</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="1">
         <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="16">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="16" t="s">
+      <c r="B47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="1">
         <v>31926</v>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="1">
         <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="16">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="16" t="s">
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="1">
         <v>34205</v>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="1">
         <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="16">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="16" t="s">
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="1">
         <v>346394</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="1">
         <v>496</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="16">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="16" t="s">
+      <c r="B50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="1">
         <v>9386</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="1">
         <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="16">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="16" t="s">
+      <c r="B51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="1">
         <v>49842</v>
       </c>
-      <c r="F51" s="16">
+      <c r="F51" s="1">
         <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="16">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="16" t="s">
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="1">
         <v>89445</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="1">
         <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="16">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="16" t="s">
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="1">
         <v>115566</v>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="1">
         <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="16">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="16" t="s">
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D54" s="16" t="s">
+      <c r="D54" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="1">
         <v>64633</v>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="1">
         <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="16">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="16" t="s">
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D55" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="1">
         <v>294684</v>
       </c>
-      <c r="F55" s="16">
+      <c r="F55" s="1">
         <v>354</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="16">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="16" t="s">
+      <c r="B56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D56" s="16" t="s">
+      <c r="D56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="1">
         <v>30231</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="1">
         <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="16">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="16" t="s">
+      <c r="B57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D57" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="1">
         <v>14082</v>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="1">
         <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="16">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="16" t="s">
+      <c r="B58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D58" s="16" t="s">
+      <c r="D58" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="1">
         <v>22760</v>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="1">
         <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="16">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="16" t="s">
+      <c r="B59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D59" s="16" t="s">
+      <c r="D59" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="1">
         <v>6335</v>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="1">
         <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="16">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="16" t="s">
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D60" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E60" s="16">
+      <c r="E60" s="1">
         <v>71886</v>
       </c>
-      <c r="F60" s="16">
+      <c r="F60" s="1">
         <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="16">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="16" t="s">
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D61" s="16" t="s">
+      <c r="D61" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="1">
         <v>56340</v>
       </c>
-      <c r="F61" s="16">
+      <c r="F61" s="1">
         <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="16">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="16" t="s">
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D62" s="16" t="s">
+      <c r="D62" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="1">
         <v>29473</v>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="1">
         <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="16">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="16" t="s">
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D63" s="16" t="s">
+      <c r="D63" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="1">
         <v>19649</v>
       </c>
-      <c r="F63" s="16">
+      <c r="F63" s="1">
         <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="16">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="16" t="s">
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="D64" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="1">
         <v>111674</v>
       </c>
-      <c r="F64" s="16">
+      <c r="F64" s="1">
         <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="16">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="16" t="s">
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D65" s="16" t="s">
+      <c r="D65" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="1">
         <v>188302</v>
       </c>
-      <c r="F65" s="16">
+      <c r="F65" s="1">
         <v>355</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="16">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="16" t="s">
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D66" s="16" t="s">
+      <c r="D66" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="1">
         <v>107711</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="1">
         <v>152</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="16">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="16" t="s">
+      <c r="B67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D67" s="16" t="s">
+      <c r="D67" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="1">
         <v>6310</v>
       </c>
-      <c r="F67" s="16">
+      <c r="F67" s="1">
         <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="16">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="16" t="s">
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D68" s="16" t="s">
+      <c r="D68" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E68" s="16">
+      <c r="E68" s="1">
         <v>32298</v>
       </c>
-      <c r="F68" s="16">
+      <c r="F68" s="1">
         <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="16">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="16" t="s">
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D69" s="16" t="s">
+      <c r="D69" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="1">
         <v>93313</v>
       </c>
-      <c r="F69" s="16">
+      <c r="F69" s="1">
         <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="16">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="B70" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="16" t="s">
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D70" s="16" t="s">
+      <c r="D70" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="1">
         <v>103590</v>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="1">
         <v>237</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="16">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="16" t="s">
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D71" s="16" t="s">
+      <c r="D71" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E71" s="16">
+      <c r="E71" s="1">
         <v>83616</v>
       </c>
-      <c r="F71" s="16">
+      <c r="F71" s="1">
         <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="16">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="B72" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C72" s="16" t="s">
+      <c r="B72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D72" s="16" t="s">
+      <c r="D72" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E72" s="16">
+      <c r="E72" s="1">
         <v>31757</v>
       </c>
-      <c r="F72" s="16">
+      <c r="F72" s="1">
         <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="16">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="B73" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="16" t="s">
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D73" s="16" t="s">
+      <c r="D73" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E73" s="16">
+      <c r="E73" s="1">
         <v>30795</v>
       </c>
-      <c r="F73" s="16">
+      <c r="F73" s="1">
         <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="16">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="B74" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="16" t="s">
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D74" s="16" t="s">
+      <c r="D74" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E74" s="16">
+      <c r="E74" s="1">
         <v>81288</v>
       </c>
-      <c r="F74" s="16">
+      <c r="F74" s="1">
         <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="16">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C75" s="16" t="s">
+      <c r="B75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D75" s="16" t="s">
+      <c r="D75" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E75" s="16">
+      <c r="E75" s="1">
         <v>6296</v>
       </c>
-      <c r="F75" s="16">
+      <c r="F75" s="1">
         <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="16">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" s="16" t="s">
+      <c r="B76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D76" s="16" t="s">
+      <c r="D76" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E76" s="16">
+      <c r="E76" s="1">
         <v>66360</v>
       </c>
-      <c r="F76" s="16">
+      <c r="F76" s="1">
         <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="16">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="16" t="s">
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D77" s="16" t="s">
+      <c r="D77" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E77" s="16">
+      <c r="E77" s="1">
         <v>7302</v>
       </c>
-      <c r="F77" s="16">
+      <c r="F77" s="1">
         <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="16">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="16" t="s">
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D78" s="16" t="s">
+      <c r="D78" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E78" s="16">
+      <c r="E78" s="1">
         <v>18968</v>
       </c>
-      <c r="F78" s="16">
+      <c r="F78" s="1">
         <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="16">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C79" s="16" t="s">
+      <c r="B79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="16" t="s">
+      <c r="D79" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E79" s="16">
+      <c r="E79" s="1">
         <v>30577</v>
       </c>
-      <c r="F79" s="16">
+      <c r="F79" s="1">
         <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="16">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="16" t="s">
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D80" s="16" t="s">
+      <c r="D80" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E80" s="16">
+      <c r="E80" s="1">
         <v>57056</v>
       </c>
-      <c r="F80" s="16">
+      <c r="F80" s="1">
         <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="16">
+      <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="B81" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" s="16" t="s">
+      <c r="B81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D81" s="16" t="s">
+      <c r="D81" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E81" s="16">
+      <c r="E81" s="1">
         <v>17399</v>
       </c>
-      <c r="F81" s="16">
+      <c r="F81" s="1">
         <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="16">
+      <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="B82" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="16" t="s">
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D82" s="16" t="s">
+      <c r="D82" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E82" s="16">
+      <c r="E82" s="1">
         <v>244965</v>
       </c>
-      <c r="F82" s="16">
+      <c r="F82" s="1">
         <v>306</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="16">
+      <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="B83" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C83" s="16" t="s">
+      <c r="B83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D83" s="16" t="s">
+      <c r="D83" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E83" s="16">
+      <c r="E83" s="1">
         <v>311864</v>
       </c>
-      <c r="F83" s="16">
+      <c r="F83" s="1">
         <v>638</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="16">
+      <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="B84" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="16" t="s">
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D84" s="16" t="s">
+      <c r="D84" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E84" s="16">
+      <c r="E84" s="1">
         <v>12793</v>
       </c>
-      <c r="F84" s="16">
+      <c r="F84" s="1">
         <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="16">
+      <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="B85" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="16" t="s">
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D85" s="16" t="s">
+      <c r="D85" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E85" s="16">
+      <c r="E85" s="1">
         <v>52132</v>
       </c>
-      <c r="F85" s="16">
+      <c r="F85" s="1">
         <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="16">
+      <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="B86" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C86" s="16" t="s">
+      <c r="B86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D86" s="16" t="s">
+      <c r="D86" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E86" s="16">
+      <c r="E86" s="1">
         <v>10482</v>
       </c>
-      <c r="F86" s="16">
+      <c r="F86" s="1">
         <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="16">
+      <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="B87" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C87" s="16" t="s">
+      <c r="B87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D87" s="16" t="s">
+      <c r="D87" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E87" s="16">
+      <c r="E87" s="1">
         <v>50223</v>
       </c>
-      <c r="F87" s="16">
+      <c r="F87" s="1">
         <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="16">
+      <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="B88" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C88" s="16" t="s">
+      <c r="B88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D88" s="16" t="s">
+      <c r="D88" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E88" s="16">
+      <c r="E88" s="1">
         <v>11007</v>
       </c>
-      <c r="F88" s="16">
+      <c r="F88" s="1">
         <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="16">
+      <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="B89" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89" s="16" t="s">
+      <c r="B89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D89" s="16" t="s">
+      <c r="D89" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E89" s="16">
+      <c r="E89" s="1">
         <v>3036</v>
       </c>
-      <c r="F89" s="16">
+      <c r="F89" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="16">
+      <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="B90" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" s="16" t="s">
+      <c r="B90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D90" s="16" t="s">
+      <c r="D90" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E90" s="16">
+      <c r="E90" s="1">
         <v>40271</v>
       </c>
-      <c r="F90" s="16">
+      <c r="F90" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="16">
+      <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="B91" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="16" t="s">
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D91" s="16" t="s">
+      <c r="D91" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E91" s="16">
+      <c r="E91" s="1">
         <v>61019</v>
       </c>
-      <c r="F91" s="16">
+      <c r="F91" s="1">
         <v>58</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="16">
+      <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="B92" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="16" t="s">
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D92" s="16" t="s">
+      <c r="D92" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E92" s="16">
+      <c r="E92" s="1">
         <v>38480</v>
       </c>
-      <c r="F92" s="16">
+      <c r="F92" s="1">
         <v>83</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="16">
+      <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="B93" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" s="16" t="s">
+      <c r="B93" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D93" s="16" t="s">
+      <c r="D93" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E93" s="16">
+      <c r="E93" s="1">
         <v>15504</v>
       </c>
-      <c r="F93" s="16">
+      <c r="F93" s="1">
         <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="16">
+      <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="B94" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="16" t="s">
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D94" s="16" t="s">
+      <c r="D94" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E94" s="16">
+      <c r="E94" s="1">
         <v>8140</v>
       </c>
-      <c r="F94" s="16">
+      <c r="F94" s="1">
         <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="16">
+      <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="B95" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="16" t="s">
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D95" s="16" t="s">
+      <c r="D95" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E95" s="16">
+      <c r="E95" s="1">
         <v>8954</v>
       </c>
-      <c r="F95" s="16">
+      <c r="F95" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="16">
+      <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="B96" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C96" s="16" t="s">
+      <c r="B96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D96" s="16" t="s">
+      <c r="D96" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E96" s="16">
+      <c r="E96" s="1">
         <v>18988</v>
       </c>
-      <c r="F96" s="16">
+      <c r="F96" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="16">
+      <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="B97" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C97" s="16" t="s">
+      <c r="B97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D97" s="16" t="s">
+      <c r="D97" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E97" s="16">
+      <c r="E97" s="1">
         <v>62372</v>
       </c>
-      <c r="F97" s="16">
+      <c r="F97" s="1">
         <v>86</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="16">
+      <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="B98" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" s="16" t="s">
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D98" s="16" t="s">
+      <c r="D98" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E98" s="16">
+      <c r="E98" s="1">
         <v>128995</v>
       </c>
-      <c r="F98" s="16">
+      <c r="F98" s="1">
         <v>182</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="16">
+      <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="B99" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C99" s="16" t="s">
+      <c r="B99" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D99" s="16" t="s">
+      <c r="D99" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E99" s="16">
+      <c r="E99" s="1">
         <v>144999</v>
       </c>
-      <c r="F99" s="16">
+      <c r="F99" s="1">
         <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="16">
+      <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="B100" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C100" s="16" t="s">
+      <c r="B100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D100" s="16" t="s">
+      <c r="D100" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E100" s="16">
+      <c r="E100" s="1">
         <v>16930</v>
       </c>
-      <c r="F100" s="16">
+      <c r="F100" s="1">
         <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="16">
+      <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="B101" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="16" t="s">
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D101" s="16" t="s">
+      <c r="D101" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E101" s="16">
+      <c r="E101" s="1">
         <v>30069</v>
       </c>
-      <c r="F101" s="16">
+      <c r="F101" s="1">
         <v>72</v>
       </c>
     </row>
@@ -3126,94 +3057,2081 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E959655-8CED-4056-8AA6-F0896203264F}">
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1">
+        <v>41152</v>
+      </c>
+      <c r="F2" s="1">
+        <v>153</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1">
+        <v>196620</v>
+      </c>
+      <c r="F3" s="1">
+        <v>754</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1">
+        <v>347205</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1397</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I4" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1">
+        <v>483400</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1039</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I5" s="3">
+        <f>COUNTIF(B1:B100,"PASS")/100</f>
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1">
+        <v>306564</v>
+      </c>
+      <c r="F6" s="1">
+        <v>384</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I6" s="1">
+        <v>17647578</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1">
+        <v>52154</v>
+      </c>
+      <c r="F7" s="1">
+        <v>227</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I7" s="1">
+        <v>54917</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1">
+        <v>568240</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2149</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I8" s="1">
+        <f>AVERAGE(E1:E100)</f>
+        <v>177966.05050505052</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1">
+        <v>242688</v>
+      </c>
+      <c r="F9" s="1">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1">
+        <v>160083</v>
+      </c>
+      <c r="F10" s="1">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1">
+        <v>21453</v>
+      </c>
+      <c r="F11" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="1">
+        <v>52433</v>
+      </c>
+      <c r="F12" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="1">
+        <v>95736</v>
+      </c>
+      <c r="F13" s="1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="1">
+        <v>33996</v>
+      </c>
+      <c r="F14" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="1">
+        <v>9251</v>
+      </c>
+      <c r="F15" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="1">
+        <v>280225</v>
+      </c>
+      <c r="F16" s="1">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="1">
+        <v>335583</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="1">
+        <v>125245</v>
+      </c>
+      <c r="F18" s="1">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="1">
+        <v>205823</v>
+      </c>
+      <c r="F19" s="1">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="1">
+        <v>152368</v>
+      </c>
+      <c r="F20" s="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="1">
+        <v>7939</v>
+      </c>
+      <c r="F21" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="D22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="1">
+        <v>94483</v>
+      </c>
+      <c r="F22" s="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="1">
+        <v>9437</v>
+      </c>
+      <c r="F23" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="1">
+        <v>7560</v>
+      </c>
+      <c r="F24" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="1">
+        <v>118693</v>
+      </c>
+      <c r="F25" s="1">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="1">
+        <v>64753</v>
+      </c>
+      <c r="F26" s="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="1">
+        <v>132654</v>
+      </c>
+      <c r="F27" s="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="1">
+        <v>33130</v>
+      </c>
+      <c r="F28" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B2" s="4">
-        <v>5071989</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="D29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="1">
+        <v>223399</v>
+      </c>
+      <c r="F29" s="1">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="1">
+        <v>332214</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="1">
+        <v>377180</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="1">
+        <v>17599</v>
+      </c>
+      <c r="F32" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="1">
+        <v>71738</v>
+      </c>
+      <c r="F33" s="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="1">
+        <v>123119</v>
+      </c>
+      <c r="F34" s="1">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="D35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" s="1">
+        <v>141683</v>
+      </c>
+      <c r="F35" s="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="1">
+        <v>146838</v>
+      </c>
+      <c r="F36" s="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="1">
+        <v>182955</v>
+      </c>
+      <c r="F37" s="1">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E38" s="1">
+        <v>379625</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="1">
+        <v>234250</v>
+      </c>
+      <c r="F39" s="1">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="7">
-        <v>411630</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="D40" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="1">
+        <v>11269</v>
+      </c>
+      <c r="F40" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="D41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="1">
+        <v>228030</v>
+      </c>
+      <c r="F41" s="1">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" s="1">
+        <v>214711</v>
+      </c>
+      <c r="F42" s="1">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="1">
+        <v>23539</v>
+      </c>
+      <c r="F43" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="1">
+        <v>191536</v>
+      </c>
+      <c r="F44" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" s="1">
+        <v>282868</v>
+      </c>
+      <c r="F45" s="1">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="1">
+        <v>39143</v>
+      </c>
+      <c r="F46" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E47" s="1">
+        <v>154778</v>
+      </c>
+      <c r="F47" s="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="10">
-        <v>316228</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="D48" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" s="1">
+        <v>85379</v>
+      </c>
+      <c r="F48" s="1">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E49" s="1">
+        <v>127035</v>
+      </c>
+      <c r="F49" s="1">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="1">
+        <v>17685</v>
+      </c>
+      <c r="F50" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E51" s="1">
+        <v>286417</v>
+      </c>
+      <c r="F51" s="1">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="1">
+        <v>180397</v>
+      </c>
+      <c r="F52" s="1">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" s="1">
+        <v>196895</v>
+      </c>
+      <c r="F53" s="1">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="D54" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" s="1">
+        <v>253112</v>
+      </c>
+      <c r="F54" s="1">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="1">
+        <v>497942</v>
+      </c>
+      <c r="F55" s="1">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E56" s="1">
+        <v>109471</v>
+      </c>
+      <c r="F56" s="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E57" s="1">
+        <v>90228</v>
+      </c>
+      <c r="F57" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E58" s="1">
+        <v>77688</v>
+      </c>
+      <c r="F58" s="1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E59" s="1">
+        <v>83713</v>
+      </c>
+      <c r="F59" s="1">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="13">
-        <v>196904</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D60" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E60" s="1">
+        <v>395080</v>
+      </c>
+      <c r="F60" s="1">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E61" s="1">
+        <v>369724</v>
+      </c>
+      <c r="F61" s="1">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E62" s="1">
+        <v>40873</v>
+      </c>
+      <c r="F62" s="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E63" s="1">
+        <v>33937</v>
+      </c>
+      <c r="F63" s="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="D64" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="1">
+        <v>527049</v>
+      </c>
+      <c r="F64" s="1">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E65" s="1">
+        <v>285291</v>
+      </c>
+      <c r="F65" s="1">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E66" s="1">
+        <v>153021</v>
+      </c>
+      <c r="F66" s="1">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" s="1">
+        <v>71793</v>
+      </c>
+      <c r="F67" s="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E68" s="1">
+        <v>32881</v>
+      </c>
+      <c r="F68" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E69" s="1">
+        <v>666381</v>
+      </c>
+      <c r="F69" s="1">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E70" s="1">
+        <v>203097</v>
+      </c>
+      <c r="F70" s="1">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E71" s="1">
+        <v>144158</v>
+      </c>
+      <c r="F71" s="1">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E72" s="1">
+        <v>107736</v>
+      </c>
+      <c r="F72" s="1">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E73" s="1">
+        <v>128570</v>
+      </c>
+      <c r="F73" s="1">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E74" s="1">
+        <v>269659</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E75" s="1">
+        <v>34231</v>
+      </c>
+      <c r="F75" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E76" s="1">
+        <v>228507</v>
+      </c>
+      <c r="F76" s="1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E77" s="1">
+        <v>36333</v>
+      </c>
+      <c r="F77" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="D78" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E78" s="1">
+        <v>83733</v>
+      </c>
+      <c r="F78" s="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E79" s="1">
+        <v>139639</v>
+      </c>
+      <c r="F79" s="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="15">
-        <v>8902</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="D80" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E80" s="1">
+        <v>541522</v>
+      </c>
+      <c r="F80" s="1">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" s="1">
+        <v>53917</v>
+      </c>
+      <c r="F81" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="D82" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E82" s="1">
+        <v>780874</v>
+      </c>
+      <c r="F82" s="1">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E83" s="1">
+        <v>171656</v>
+      </c>
+      <c r="F83" s="1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E84" s="1">
+        <v>53921</v>
+      </c>
+      <c r="F84" s="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E85" s="1">
+        <v>312035</v>
+      </c>
+      <c r="F85" s="1">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E86" s="1">
+        <v>118142</v>
+      </c>
+      <c r="F86" s="1">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E87" s="1">
+        <v>140172</v>
+      </c>
+      <c r="F87" s="1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E88" s="1">
+        <v>59896</v>
+      </c>
+      <c r="F88" s="1">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E89" s="1">
+        <v>21312</v>
+      </c>
+      <c r="F89" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E90" s="1">
+        <v>223286</v>
+      </c>
+      <c r="F90" s="1">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E91" s="1">
+        <v>246159</v>
+      </c>
+      <c r="F91" s="1">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E92" s="1">
+        <v>190941</v>
+      </c>
+      <c r="F92" s="1">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>181</v>
       </c>
+      <c r="D93" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E93" s="1">
+        <v>28069</v>
+      </c>
+      <c r="F93" s="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E94" s="1">
+        <v>94642</v>
+      </c>
+      <c r="F94" s="1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E95" s="1">
+        <v>24326</v>
+      </c>
+      <c r="F95" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E96" s="1">
+        <v>82674</v>
+      </c>
+      <c r="F96" s="1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E97" s="1">
+        <v>276609</v>
+      </c>
+      <c r="F97" s="1">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E98" s="1">
+        <v>415511</v>
+      </c>
+      <c r="F98" s="1">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E99" s="1">
+        <v>208143</v>
+      </c>
+      <c r="F99" s="1">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E100" s="1">
+        <v>61835</v>
+      </c>
+      <c r="F100" s="1">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E101" s="1">
+        <v>28939</v>
+      </c>
+      <c r="F101" s="1">
+        <v>113</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>